--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92537088264</v>
+        <v>46157.93110517311</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110517311</v>
+        <v>46157.93365875341</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93365875341</v>
+        <v>46157.93667964828</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93667964828</v>
+        <v>46158.28192379246</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28192379246</v>
+        <v>46158.29713483262</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713483262</v>
+        <v>46158.2978777972</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2978777972</v>
+        <v>46158.33353874269</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33353874269</v>
+        <v>46158.3720952597</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Черновики_и_служебное/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3720952597</v>
+        <v>46158.3742857802</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
